--- a/Godknows_Mutize/Mutize_Ex3A_tables.xlsx
+++ b/Godknows_Mutize/Mutize_Ex3A_tables.xlsx
@@ -8,46 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1aadc79da8212a75/Documents/DATA_Labs/W2_Workshop/Godknows_Mutize/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_F25DC773A252ABDACC104821C19E64105BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF96341-698F-4F87-A7D2-D6DFC97DCBB8}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_F25DC773A252ABDACC104821C19E64105BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F376C0-014E-4513-B421-CE5049D7558E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3195" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Clients" sheetId="1" r:id="rId1"/>
-    <sheet name="Walkers" sheetId="2" r:id="rId2"/>
-    <sheet name="Dogs" sheetId="3" r:id="rId3"/>
-    <sheet name="Walks" sheetId="4" r:id="rId4"/>
-    <sheet name="Dog_Walk" sheetId="5" r:id="rId5"/>
+    <sheet name="clients" sheetId="1" r:id="rId1"/>
+    <sheet name="walkers" sheetId="2" r:id="rId2"/>
+    <sheet name="dogs" sheetId="3" r:id="rId3"/>
+    <sheet name="walks" sheetId="4" r:id="rId4"/>
+    <sheet name="dog_walk" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
-  <si>
-    <t>Client_ID</t>
-  </si>
-  <si>
-    <t>First_Name</t>
-  </si>
-  <si>
-    <t>Last_Name</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>walker_id</t>
   </si>
@@ -100,17 +93,79 @@
     <t>status</t>
   </si>
   <si>
-    <t>dog_walk_id</t>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>sarah@gmail.com</t>
+  </si>
+  <si>
+    <t>Fred</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>fred@gmail.com</t>
+  </si>
+  <si>
+    <t>321 Stacy Rd</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>Mon-Fri</t>
+  </si>
+  <si>
+    <t>Lunah</t>
+  </si>
+  <si>
+    <t>Bull dog</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>7201 Columbia Falls</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -145,15 +200,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -432,33 +493,120 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>5643344</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>4546575</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{43650B86-0232-4707-A0C5-E4D156097680}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{F7B7D67D-145A-45A8-B01D-9CFC28884229}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FBC68E-3015-48BE-B81D-DFB7B601CE54}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>5643267</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -466,16 +614,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FBC68E-3015-48BE-B81D-DFB7B601CE54}">
-  <dimension ref="A1:E1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0192F156-C94E-4826-B605-B6D613BBEA3F}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -494,34 +636,81 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0192F156-C94E-4826-B605-B6D613BBEA3F}">
-  <dimension ref="A1:F1"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E83C14-5F27-49D8-81E0-2A2E96A3E959}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5">
+        <v>45306</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -529,63 +718,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E83C14-5F27-49D8-81E0-2A2E96A3E959}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1A1C2C-5FF9-4C90-9C04-00535F2E414A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
